--- a/templates/contract.xlsx
+++ b/templates/contract.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27932"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2461A79-7C6A-4DB2-BFEA-629EA49DA4D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4A3C3F8-1E97-4277-9830-EAF005E487D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39540" yWindow="1140" windowWidth="19200" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39540" yWindow="1140" windowWidth="21600" windowHeight="11175" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet1" sheetId="1" r:id="rId1"/>
@@ -27,6 +27,28 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata">
+  <metadataTypes count="1">
+    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLRICHVALUE" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
+          <xlrd:rvb i="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <valueMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </valueMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
   <si>
@@ -226,14 +248,6 @@
       </rPr>
       <t>: 익년 2월 1일부터 3월 31일까지</t>
     </r>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>박 성준</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>경기도 화성시 마도면 해운로 729</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -288,27 +302,35 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>(계약금은 기부에 사용될 물품 구입에 사용됩니다.)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>주식회사 한울파운데이션; 동양MF</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>449-81-03458; 177-06-02178</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>010-9593-9862</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>제3조 계약금(당해년도 예상 환급금의 5%를 계약금으로 한다)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>계약 체결일로부터 7일 이내</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>인디코어</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>김 도훈</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>650-15-01865</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>010-3561-7528</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>(계약금은 기부에 사용될 물품 구입에 사용됩니다.-가입 첫해는 계약금 없이 진행 됩니다.)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>서울시 서초구 서초대로54길 29-20</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -696,59 +718,68 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>22093</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>3173</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F243048D-4C78-2479-7AF1-C969CFFB8519}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4946518" y="9734550"/>
-          <a:ext cx="635132" cy="669923"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
+<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <global>
+    <keyFlags>
+      <key name="_Self">
+        <flag name="ExcludeFromFile" value="1"/>
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_DisplayString">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Flags">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Format">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_SubLabel">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Attribution">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Icon">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_Display">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_CanonicalPropertyNames">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+      <key name="_ClassificationId">
+        <flag name="ExcludeFromCalcComparison" value="1"/>
+      </key>
+    </keyFlags>
+  </global>
+</rvTypesInfo>
+</file>
+
+<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
+<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <rv s="0">
+    <v>5</v>
+    <v>0</v>
+  </rv>
+</rvData>
+</file>
+
+<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
+<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="1">
+  <s t="_localImage">
+    <k n="CalcOrigin" t="i"/>
+    <k n="_rvRel:LocalImageIdentifier" t="i"/>
+  </s>
+</rvStructures>
+</file>
+
+<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
+<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <rel r:id="rId1"/>
+</richValueRels>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1106,7 +1137,7 @@
         <v>8</v>
       </c>
       <c r="E5" s="46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F5" s="46"/>
       <c r="G5" s="46"/>
@@ -1126,7 +1157,7 @@
         <v>8</v>
       </c>
       <c r="E6" s="46" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F6" s="46"/>
       <c r="G6" s="46"/>
@@ -1146,7 +1177,7 @@
         <v>8</v>
       </c>
       <c r="E7" s="46" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="F7" s="46"/>
       <c r="G7" s="46"/>
@@ -1318,7 +1349,7 @@
       <c r="A17" s="34"/>
       <c r="B17" s="5"/>
       <c r="C17" s="47" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D17" s="47"/>
       <c r="E17" s="47"/>
@@ -1417,7 +1448,7 @@
     <row r="23" spans="1:12" s="25" customFormat="1" ht="25.25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A23" s="36"/>
       <c r="B23" s="28" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="C23" s="26"/>
       <c r="D23" s="26"/>
@@ -1438,7 +1469,7 @@
       </c>
       <c r="D24" s="12"/>
       <c r="E24" s="12" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F24" s="12"/>
       <c r="G24" s="12"/>
@@ -1460,7 +1491,7 @@
       </c>
       <c r="D25" s="12"/>
       <c r="E25" s="12" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F25" s="12"/>
       <c r="G25" s="12"/>
@@ -1490,7 +1521,7 @@
       <c r="A27" s="22"/>
       <c r="B27" s="29"/>
       <c r="C27" s="15" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
@@ -1554,7 +1585,7 @@
       <c r="A31" s="22"/>
       <c r="B31" s="16"/>
       <c r="C31" s="16" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D31" s="12"/>
       <c r="E31" s="23"/>
@@ -1599,7 +1630,7 @@
     <row r="34" spans="1:12" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.45">
       <c r="A34" s="19"/>
       <c r="B34" s="30" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C34" s="12"/>
       <c r="D34" s="12"/>
@@ -1615,7 +1646,7 @@
     <row r="35" spans="1:12" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.45">
       <c r="A35" s="19"/>
       <c r="B35" s="30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C35" s="12"/>
       <c r="D35" s="12"/>
@@ -1631,7 +1662,7 @@
     <row r="36" spans="1:12" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.45">
       <c r="A36" s="19"/>
       <c r="B36" s="30" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
@@ -1761,13 +1792,15 @@
         <v>30</v>
       </c>
       <c r="F44" s="55" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G44" s="55"/>
       <c r="H44" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="I44" s="57"/>
+      <c r="I44" s="57" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
       <c r="J44" s="57"/>
       <c r="K44" s="21"/>
       <c r="L44" s="38"/>
@@ -1810,7 +1843,7 @@
       <c r="A47" s="19"/>
       <c r="B47" s="31"/>
       <c r="C47" s="53" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D47" s="53"/>
       <c r="E47" s="53"/>
@@ -1872,6 +1905,5 @@
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.43307086614173229" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="82" orientation="portrait" useFirstPageNumber="1" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>